--- a/magic_formula_ranked.xlsx
+++ b/magic_formula_ranked.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Magic_Formula_Rank</t>
+          <t>MF_Rank</t>
         </is>
       </c>
     </row>
